--- a/mosip_master/xlsx/applicant_valid_document.xlsx
+++ b/mosip_master/xlsx/applicant_valid_document.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Sao-Tome-mosip-master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2582A0E2-479B-44FC-9D74-C295368B01AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A477BE-CD91-46A1-8D7A-9950EBF28767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$253</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="44">
   <si>
     <t>lang_code</t>
   </si>
@@ -142,9 +142,6 @@
   </si>
   <si>
     <t>CBT</t>
-  </si>
-  <si>
-    <t>ACM</t>
   </si>
   <si>
     <t>CCM</t>
@@ -542,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E279"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="8.453125" style="1"/>
@@ -611,7 +608,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
@@ -622,13 +619,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>7</v>
@@ -642,10 +639,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>7</v>
@@ -659,10 +656,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>7</v>
@@ -673,13 +670,13 @@
         <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>7</v>
@@ -690,13 +687,13 @@
         <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>7</v>
@@ -710,10 +707,10 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>7</v>
@@ -724,13 +721,13 @@
         <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>7</v>
@@ -741,13 +738,13 @@
         <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>7</v>
@@ -758,7 +755,7 @@
         <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
@@ -775,13 +772,13 @@
         <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>7</v>
@@ -792,13 +789,13 @@
         <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>7</v>
@@ -809,13 +806,13 @@
         <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>7</v>
@@ -826,13 +823,13 @@
         <v>27</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>7</v>
@@ -843,7 +840,7 @@
         <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
         <v>6</v>
@@ -860,7 +857,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
@@ -877,13 +874,13 @@
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>7</v>
@@ -894,13 +891,13 @@
         <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>7</v>
@@ -911,13 +908,13 @@
         <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>7</v>
@@ -928,13 +925,13 @@
         <v>27</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>7</v>
@@ -945,13 +942,13 @@
         <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>7</v>
@@ -962,7 +959,7 @@
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
         <v>6</v>
@@ -979,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>7</v>
@@ -996,13 +993,13 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>7</v>
@@ -1013,7 +1010,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C28" t="s">
         <v>6</v>
@@ -1030,13 +1027,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>7</v>
@@ -1047,13 +1044,13 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>7</v>
@@ -1064,13 +1061,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>7</v>
@@ -1081,13 +1078,13 @@
         <v>27</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>7</v>
@@ -1098,13 +1095,13 @@
         <v>27</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>7</v>
@@ -1115,13 +1112,13 @@
         <v>27</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>7</v>
@@ -1132,13 +1129,13 @@
         <v>27</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>7</v>
@@ -1149,13 +1146,13 @@
         <v>27</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>7</v>
@@ -1166,13 +1163,13 @@
         <v>27</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>7</v>
@@ -1183,13 +1180,13 @@
         <v>27</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>7</v>
@@ -1200,13 +1197,13 @@
         <v>27</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>7</v>
@@ -1217,13 +1214,13 @@
         <v>27</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>7</v>
@@ -1234,13 +1231,13 @@
         <v>27</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>7</v>
@@ -1251,13 +1248,13 @@
         <v>27</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>7</v>
@@ -1268,13 +1265,13 @@
         <v>27</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>7</v>
@@ -1285,13 +1282,13 @@
         <v>27</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>7</v>
@@ -1302,13 +1299,13 @@
         <v>27</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>7</v>
@@ -1319,13 +1316,13 @@
         <v>27</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>7</v>
@@ -1336,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
         <v>8</v>
@@ -1353,13 +1350,13 @@
         <v>27</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>7</v>
@@ -1370,13 +1367,13 @@
         <v>27</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>7</v>
@@ -1387,13 +1384,13 @@
         <v>27</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>7</v>
@@ -1407,10 +1404,10 @@
         <v>24</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>7</v>
@@ -1421,13 +1418,13 @@
         <v>27</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>7</v>
@@ -1438,13 +1435,13 @@
         <v>27</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>7</v>
@@ -1455,13 +1452,13 @@
         <v>27</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>7</v>
@@ -1472,13 +1469,13 @@
         <v>27</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C55" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>7</v>
@@ -1489,13 +1486,13 @@
         <v>27</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>7</v>
@@ -1506,13 +1503,13 @@
         <v>27</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>7</v>
@@ -1523,13 +1520,13 @@
         <v>27</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C58" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>7</v>
@@ -1540,13 +1537,13 @@
         <v>27</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>7</v>
@@ -1557,13 +1554,13 @@
         <v>27</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>7</v>
@@ -1574,7 +1571,7 @@
         <v>27</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
         <v>8</v>
@@ -1591,7 +1588,7 @@
         <v>27</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
@@ -1608,7 +1605,7 @@
         <v>27</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
@@ -1625,7 +1622,7 @@
         <v>27</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
         <v>8</v>
@@ -1642,7 +1639,7 @@
         <v>27</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C65" t="s">
         <v>8</v>
@@ -1659,7 +1656,7 @@
         <v>27</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C66" t="s">
         <v>8</v>
@@ -1676,7 +1673,7 @@
         <v>27</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
         <v>8</v>
@@ -1693,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>7</v>
@@ -1710,13 +1707,13 @@
         <v>27</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C69" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>7</v>
@@ -1727,13 +1724,13 @@
         <v>27</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>7</v>
@@ -1744,13 +1741,13 @@
         <v>27</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>7</v>
@@ -1761,13 +1758,13 @@
         <v>27</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C72" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>7</v>
@@ -1778,13 +1775,13 @@
         <v>27</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C73" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>7</v>
@@ -1795,13 +1792,13 @@
         <v>27</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C74" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>7</v>
@@ -1812,13 +1809,13 @@
         <v>27</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C75" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>7</v>
@@ -1829,13 +1826,13 @@
         <v>27</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C76" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>7</v>
@@ -1846,7 +1843,7 @@
         <v>27</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
         <v>8</v>
@@ -1863,7 +1860,7 @@
         <v>27</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
         <v>8</v>
@@ -1880,7 +1877,7 @@
         <v>27</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C79" t="s">
         <v>8</v>
@@ -1897,7 +1894,7 @@
         <v>27</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C80" t="s">
         <v>8</v>
@@ -1914,7 +1911,7 @@
         <v>27</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C81" t="s">
         <v>8</v>
@@ -1931,7 +1928,7 @@
         <v>27</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -1948,7 +1945,7 @@
         <v>27</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -1965,13 +1962,13 @@
         <v>27</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C84" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>7</v>
@@ -1982,13 +1979,13 @@
         <v>27</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>7</v>
@@ -1999,13 +1996,13 @@
         <v>27</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>7</v>
@@ -2016,13 +2013,13 @@
         <v>27</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>7</v>
@@ -2033,13 +2030,13 @@
         <v>27</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>7</v>
@@ -2050,13 +2047,13 @@
         <v>27</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C89" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>7</v>
@@ -2067,13 +2064,13 @@
         <v>27</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>7</v>
@@ -2084,13 +2081,13 @@
         <v>27</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>7</v>
@@ -2101,13 +2098,13 @@
         <v>27</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>7</v>
@@ -2118,7 +2115,7 @@
         <v>27</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C93" t="s">
         <v>6</v>
@@ -2135,7 +2132,7 @@
         <v>27</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C94" t="s">
         <v>6</v>
@@ -2152,7 +2149,7 @@
         <v>27</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C95" t="s">
         <v>6</v>
@@ -2169,7 +2166,7 @@
         <v>27</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C96" t="s">
         <v>6</v>
@@ -2186,7 +2183,7 @@
         <v>27</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C97" t="s">
         <v>6</v>
@@ -2203,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C98" t="s">
         <v>6</v>
@@ -2220,7 +2217,7 @@
         <v>27</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C99" t="s">
         <v>6</v>
@@ -2237,7 +2234,7 @@
         <v>27</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C100" t="s">
         <v>6</v>
@@ -2254,13 +2251,13 @@
         <v>27</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C101" t="s">
         <v>6</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>7</v>
@@ -2271,13 +2268,13 @@
         <v>27</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C102" t="s">
         <v>6</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>7</v>
@@ -2288,13 +2285,13 @@
         <v>27</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
         <v>6</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>7</v>
@@ -2305,13 +2302,13 @@
         <v>27</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C104" t="s">
         <v>6</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>7</v>
@@ -2322,13 +2319,13 @@
         <v>27</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
         <v>6</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>7</v>
@@ -2339,13 +2336,13 @@
         <v>27</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
         <v>6</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>7</v>
@@ -2356,13 +2353,13 @@
         <v>27</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C107" t="s">
         <v>6</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>7</v>
@@ -2373,13 +2370,13 @@
         <v>27</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C108" t="s">
         <v>6</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>7</v>
@@ -2390,13 +2387,13 @@
         <v>27</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C109" t="s">
         <v>6</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>7</v>
@@ -2407,7 +2404,7 @@
         <v>27</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C110" t="s">
         <v>6</v>
@@ -2424,7 +2421,7 @@
         <v>27</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C111" t="s">
         <v>6</v>
@@ -2441,7 +2438,7 @@
         <v>27</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C112" t="s">
         <v>6</v>
@@ -2458,7 +2455,7 @@
         <v>27</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C113" t="s">
         <v>6</v>
@@ -2475,7 +2472,7 @@
         <v>27</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C114" t="s">
         <v>6</v>
@@ -2492,7 +2489,7 @@
         <v>27</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C115" t="s">
         <v>6</v>
@@ -2509,7 +2506,7 @@
         <v>27</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C116" t="s">
         <v>6</v>
@@ -2526,7 +2523,7 @@
         <v>27</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C117" t="s">
         <v>6</v>
@@ -2543,13 +2540,13 @@
         <v>27</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C118" t="s">
         <v>6</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>7</v>
@@ -2560,13 +2557,13 @@
         <v>27</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C119" t="s">
         <v>6</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>7</v>
@@ -2577,13 +2574,13 @@
         <v>27</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C120" t="s">
         <v>6</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>7</v>
@@ -2594,13 +2591,13 @@
         <v>27</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
         <v>6</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>7</v>
@@ -2611,13 +2608,13 @@
         <v>27</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
         <v>6</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>7</v>
@@ -2628,13 +2625,13 @@
         <v>27</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C123" t="s">
         <v>6</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>7</v>
@@ -2645,13 +2642,13 @@
         <v>27</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C124" t="s">
         <v>6</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>7</v>
@@ -2662,13 +2659,13 @@
         <v>27</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C125" t="s">
         <v>6</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>7</v>
@@ -2679,13 +2676,13 @@
         <v>27</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C126" t="s">
         <v>6</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>7</v>
@@ -2696,7 +2693,7 @@
         <v>27</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C127" t="s">
         <v>6</v>
@@ -2713,7 +2710,7 @@
         <v>27</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C128" t="s">
         <v>6</v>
@@ -2730,7 +2727,7 @@
         <v>27</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C129" t="s">
         <v>6</v>
@@ -2747,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C130" t="s">
         <v>6</v>
@@ -2764,7 +2761,7 @@
         <v>27</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C131" t="s">
         <v>6</v>
@@ -2781,7 +2778,7 @@
         <v>27</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C132" t="s">
         <v>6</v>
@@ -2798,7 +2795,7 @@
         <v>27</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C133" t="s">
         <v>6</v>
@@ -2815,7 +2812,7 @@
         <v>27</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C134" t="s">
         <v>6</v>
@@ -2832,13 +2829,13 @@
         <v>27</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C135" t="s">
         <v>6</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>7</v>
@@ -2849,13 +2846,13 @@
         <v>27</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C136" t="s">
         <v>6</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>7</v>
@@ -2866,13 +2863,13 @@
         <v>27</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
         <v>6</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>7</v>
@@ -2883,13 +2880,13 @@
         <v>27</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C138" t="s">
         <v>6</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>7</v>
@@ -2900,13 +2897,13 @@
         <v>27</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C139" t="s">
         <v>6</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>7</v>
@@ -2917,13 +2914,13 @@
         <v>27</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C140" t="s">
         <v>6</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>7</v>
@@ -2934,13 +2931,13 @@
         <v>27</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C141" t="s">
         <v>6</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>7</v>
@@ -2951,13 +2948,13 @@
         <v>27</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C142" t="s">
         <v>6</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>7</v>
@@ -2968,13 +2965,13 @@
         <v>27</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C143" t="s">
         <v>6</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>7</v>
@@ -2985,7 +2982,7 @@
         <v>27</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C144" t="s">
         <v>6</v>
@@ -3002,7 +2999,7 @@
         <v>27</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C145" t="s">
         <v>6</v>
@@ -3019,7 +3016,7 @@
         <v>27</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C146" t="s">
         <v>6</v>
@@ -3036,7 +3033,7 @@
         <v>27</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C147" t="s">
         <v>6</v>
@@ -3053,7 +3050,7 @@
         <v>27</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C148" t="s">
         <v>6</v>
@@ -3070,7 +3067,7 @@
         <v>27</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C149" t="s">
         <v>6</v>
@@ -3087,7 +3084,7 @@
         <v>27</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C150" t="s">
         <v>6</v>
@@ -3104,7 +3101,7 @@
         <v>27</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C151" t="s">
         <v>6</v>
@@ -3121,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C152" t="s">
         <v>6</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>7</v>
@@ -3138,13 +3135,13 @@
         <v>27</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C153" t="s">
         <v>6</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>7</v>
@@ -3155,13 +3152,13 @@
         <v>27</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C154" t="s">
         <v>6</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>7</v>
@@ -3172,13 +3169,13 @@
         <v>27</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C155" t="s">
         <v>6</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>7</v>
@@ -3189,13 +3186,13 @@
         <v>27</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C156" t="s">
         <v>6</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>7</v>
@@ -3206,13 +3203,13 @@
         <v>27</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C157" t="s">
         <v>6</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>7</v>
@@ -3223,13 +3220,13 @@
         <v>27</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C158" t="s">
         <v>6</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>7</v>
@@ -3240,13 +3237,13 @@
         <v>27</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C159" t="s">
         <v>6</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>7</v>
@@ -3257,13 +3254,13 @@
         <v>27</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C160" t="s">
         <v>6</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>7</v>
@@ -3274,7 +3271,7 @@
         <v>27</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C161" t="s">
         <v>6</v>
@@ -3291,7 +3288,7 @@
         <v>27</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C162" t="s">
         <v>6</v>
@@ -3308,7 +3305,7 @@
         <v>27</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C163" t="s">
         <v>6</v>
@@ -3325,7 +3322,7 @@
         <v>27</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C164" t="s">
         <v>6</v>
@@ -3342,7 +3339,7 @@
         <v>27</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C165" t="s">
         <v>6</v>
@@ -3359,7 +3356,7 @@
         <v>27</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C166" t="s">
         <v>6</v>
@@ -3376,7 +3373,7 @@
         <v>27</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C167" t="s">
         <v>6</v>
@@ -3393,7 +3390,7 @@
         <v>27</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C168" t="s">
         <v>6</v>
@@ -3410,13 +3407,13 @@
         <v>27</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C169" t="s">
         <v>6</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>7</v>
@@ -3427,13 +3424,13 @@
         <v>27</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C170" t="s">
         <v>6</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>7</v>
@@ -3444,13 +3441,13 @@
         <v>27</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C171" t="s">
         <v>6</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>7</v>
@@ -3461,13 +3458,13 @@
         <v>27</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C172" t="s">
         <v>6</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>7</v>
@@ -3478,13 +3475,13 @@
         <v>27</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C173" t="s">
         <v>6</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>7</v>
@@ -3495,13 +3492,13 @@
         <v>27</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C174" t="s">
         <v>6</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>7</v>
@@ -3512,13 +3509,13 @@
         <v>27</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C175" t="s">
         <v>6</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>7</v>
@@ -3529,13 +3526,13 @@
         <v>27</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C176" t="s">
         <v>6</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>7</v>
@@ -3546,13 +3543,13 @@
         <v>27</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C177" t="s">
         <v>6</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>7</v>
@@ -3563,7 +3560,7 @@
         <v>27</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C178" t="s">
         <v>6</v>
@@ -3580,7 +3577,7 @@
         <v>27</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C179" t="s">
         <v>6</v>
@@ -3597,7 +3594,7 @@
         <v>27</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C180" t="s">
         <v>6</v>
@@ -3614,7 +3611,7 @@
         <v>27</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C181" t="s">
         <v>6</v>
@@ -3631,7 +3628,7 @@
         <v>27</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C182" t="s">
         <v>6</v>
@@ -3648,7 +3645,7 @@
         <v>27</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C183" t="s">
         <v>6</v>
@@ -3665,7 +3662,7 @@
         <v>27</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C184" t="s">
         <v>6</v>
@@ -3682,7 +3679,7 @@
         <v>27</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C185" t="s">
         <v>6</v>
@@ -3699,13 +3696,13 @@
         <v>27</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C186" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>7</v>
@@ -3716,13 +3713,13 @@
         <v>27</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C187" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>7</v>
@@ -3733,13 +3730,13 @@
         <v>27</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C188" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>7</v>
@@ -3750,13 +3747,13 @@
         <v>27</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C189" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>7</v>
@@ -3767,13 +3764,13 @@
         <v>27</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C190" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>7</v>
@@ -3784,13 +3781,13 @@
         <v>27</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C191" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>7</v>
@@ -3801,13 +3798,13 @@
         <v>27</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C192" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>7</v>
@@ -3818,13 +3815,13 @@
         <v>27</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C193" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>7</v>
@@ -3835,13 +3832,13 @@
         <v>27</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C194" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>7</v>
@@ -3855,10 +3852,10 @@
         <v>26</v>
       </c>
       <c r="C195" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>7</v>
@@ -3872,10 +3869,10 @@
         <v>5</v>
       </c>
       <c r="C196" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>7</v>
@@ -3889,10 +3886,10 @@
         <v>11</v>
       </c>
       <c r="C197" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>7</v>
@@ -3906,10 +3903,10 @@
         <v>12</v>
       </c>
       <c r="C198" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>7</v>
@@ -3923,10 +3920,10 @@
         <v>13</v>
       </c>
       <c r="C199" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>7</v>
@@ -3940,10 +3937,10 @@
         <v>14</v>
       </c>
       <c r="C200" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>7</v>
@@ -3957,10 +3954,10 @@
         <v>15</v>
       </c>
       <c r="C201" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>7</v>
@@ -3974,10 +3971,10 @@
         <v>16</v>
       </c>
       <c r="C202" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>7</v>
@@ -3991,10 +3988,10 @@
         <v>17</v>
       </c>
       <c r="C203" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>7</v>
@@ -4008,10 +4005,10 @@
         <v>18</v>
       </c>
       <c r="C204" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>7</v>
@@ -4025,10 +4022,10 @@
         <v>19</v>
       </c>
       <c r="C205" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>7</v>
@@ -4042,10 +4039,10 @@
         <v>20</v>
       </c>
       <c r="C206" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>7</v>
@@ -4059,10 +4056,10 @@
         <v>21</v>
       </c>
       <c r="C207" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>7</v>
@@ -4076,10 +4073,10 @@
         <v>22</v>
       </c>
       <c r="C208" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>7</v>
@@ -4093,10 +4090,10 @@
         <v>23</v>
       </c>
       <c r="C209" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>7</v>
@@ -4110,10 +4107,10 @@
         <v>24</v>
       </c>
       <c r="C210" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>7</v>
@@ -4127,10 +4124,10 @@
         <v>25</v>
       </c>
       <c r="C211" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>7</v>
@@ -4144,10 +4141,10 @@
         <v>26</v>
       </c>
       <c r="C212" t="s">
-        <v>10</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="D212" t="s">
+        <v>36</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>7</v>
@@ -4161,10 +4158,10 @@
         <v>5</v>
       </c>
       <c r="C213" t="s">
-        <v>10</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="D213" t="s">
+        <v>36</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>7</v>
@@ -4175,13 +4172,13 @@
         <v>27</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C214" t="s">
-        <v>10</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="D214" t="s">
+        <v>36</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>7</v>
@@ -4192,13 +4189,13 @@
         <v>27</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C215" t="s">
-        <v>10</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="D215" t="s">
+        <v>36</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>7</v>
@@ -4209,13 +4206,13 @@
         <v>27</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C216" t="s">
-        <v>10</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="D216" t="s">
+        <v>36</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>7</v>
@@ -4226,13 +4223,13 @@
         <v>27</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C217" t="s">
-        <v>10</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="D217" t="s">
+        <v>36</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>7</v>
@@ -4243,13 +4240,13 @@
         <v>27</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C218" t="s">
-        <v>10</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="D218" t="s">
+        <v>36</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>7</v>
@@ -4260,13 +4257,13 @@
         <v>27</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C219" t="s">
-        <v>10</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="D219" t="s">
+        <v>36</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>7</v>
@@ -4277,13 +4274,13 @@
         <v>27</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C220" t="s">
-        <v>10</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
+      </c>
+      <c r="D220" t="s">
+        <v>36</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>7</v>
@@ -4294,13 +4291,13 @@
         <v>27</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C221" t="s">
         <v>9</v>
       </c>
-      <c r="D221" s="1" t="s">
-        <v>41</v>
+      <c r="D221" t="s">
+        <v>36</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>7</v>
@@ -4311,13 +4308,13 @@
         <v>27</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C222" t="s">
         <v>9</v>
       </c>
-      <c r="D222" s="1" t="s">
-        <v>41</v>
+      <c r="D222" t="s">
+        <v>36</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>7</v>
@@ -4328,13 +4325,13 @@
         <v>27</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C223" t="s">
         <v>9</v>
       </c>
-      <c r="D223" s="1" t="s">
-        <v>41</v>
+      <c r="D223" t="s">
+        <v>36</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>7</v>
@@ -4345,13 +4342,13 @@
         <v>27</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C224" t="s">
         <v>9</v>
       </c>
-      <c r="D224" s="1" t="s">
-        <v>41</v>
+      <c r="D224" t="s">
+        <v>36</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>7</v>
@@ -4362,13 +4359,13 @@
         <v>27</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C225" t="s">
         <v>9</v>
       </c>
-      <c r="D225" s="1" t="s">
-        <v>41</v>
+      <c r="D225" t="s">
+        <v>36</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>7</v>
@@ -4379,13 +4376,13 @@
         <v>27</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C226" t="s">
         <v>9</v>
       </c>
-      <c r="D226" s="1" t="s">
-        <v>41</v>
+      <c r="D226" t="s">
+        <v>36</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>7</v>
@@ -4396,13 +4393,13 @@
         <v>27</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C227" t="s">
         <v>9</v>
       </c>
-      <c r="D227" s="1" t="s">
-        <v>41</v>
+      <c r="D227" t="s">
+        <v>36</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>7</v>
@@ -4413,13 +4410,13 @@
         <v>27</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C228" t="s">
         <v>9</v>
       </c>
-      <c r="D228" s="1" t="s">
-        <v>41</v>
+      <c r="D228" t="s">
+        <v>36</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>7</v>
@@ -4430,12 +4427,12 @@
         <v>27</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C229" t="s">
         <v>9</v>
       </c>
-      <c r="D229" s="1" t="s">
+      <c r="D229" t="s">
         <v>41</v>
       </c>
       <c r="E229" s="1" t="s">
@@ -4447,12 +4444,12 @@
         <v>27</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C230" t="s">
         <v>9</v>
       </c>
-      <c r="D230" s="1" t="s">
+      <c r="D230" t="s">
         <v>41</v>
       </c>
       <c r="E230" s="1" t="s">
@@ -4464,12 +4461,12 @@
         <v>27</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C231" t="s">
         <v>9</v>
       </c>
-      <c r="D231" s="1" t="s">
+      <c r="D231" t="s">
         <v>41</v>
       </c>
       <c r="E231" s="1" t="s">
@@ -4481,12 +4478,12 @@
         <v>27</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C232" t="s">
         <v>9</v>
       </c>
-      <c r="D232" s="1" t="s">
+      <c r="D232" t="s">
         <v>41</v>
       </c>
       <c r="E232" s="1" t="s">
@@ -4498,12 +4495,12 @@
         <v>27</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C233" t="s">
         <v>9</v>
       </c>
-      <c r="D233" s="1" t="s">
+      <c r="D233" t="s">
         <v>41</v>
       </c>
       <c r="E233" s="1" t="s">
@@ -4515,12 +4512,12 @@
         <v>27</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C234" t="s">
         <v>9</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="D234" t="s">
         <v>41</v>
       </c>
       <c r="E234" s="1" t="s">
@@ -4532,12 +4529,12 @@
         <v>27</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C235" t="s">
         <v>9</v>
       </c>
-      <c r="D235" s="1" t="s">
+      <c r="D235" t="s">
         <v>41</v>
       </c>
       <c r="E235" s="1" t="s">
@@ -4549,12 +4546,12 @@
         <v>27</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C236" t="s">
         <v>9</v>
       </c>
-      <c r="D236" s="1" t="s">
+      <c r="D236" t="s">
         <v>41</v>
       </c>
       <c r="E236" s="1" t="s">
@@ -4566,12 +4563,12 @@
         <v>27</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C237" t="s">
         <v>9</v>
       </c>
-      <c r="D237" s="1" t="s">
+      <c r="D237" t="s">
         <v>41</v>
       </c>
       <c r="E237" s="1" t="s">
@@ -4583,13 +4580,13 @@
         <v>27</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C238" t="s">
         <v>9</v>
       </c>
       <c r="D238" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>7</v>
@@ -4600,13 +4597,13 @@
         <v>27</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C239" t="s">
         <v>9</v>
       </c>
       <c r="D239" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>7</v>
@@ -4617,13 +4614,13 @@
         <v>27</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C240" t="s">
         <v>9</v>
       </c>
       <c r="D240" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>7</v>
@@ -4634,13 +4631,13 @@
         <v>27</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C241" t="s">
         <v>9</v>
       </c>
       <c r="D241" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>7</v>
@@ -4651,13 +4648,13 @@
         <v>27</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C242" t="s">
         <v>9</v>
       </c>
       <c r="D242" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>7</v>
@@ -4668,13 +4665,13 @@
         <v>27</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C243" t="s">
         <v>9</v>
       </c>
       <c r="D243" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>7</v>
@@ -4685,13 +4682,13 @@
         <v>27</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C244" t="s">
         <v>9</v>
       </c>
       <c r="D244" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>7</v>
@@ -4702,13 +4699,13 @@
         <v>27</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C245" t="s">
         <v>9</v>
       </c>
       <c r="D245" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>7</v>
@@ -4719,13 +4716,13 @@
         <v>27</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C246" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D246" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>7</v>
@@ -4736,13 +4733,13 @@
         <v>27</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C247" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D247" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>7</v>
@@ -4753,13 +4750,13 @@
         <v>27</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C248" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D248" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>7</v>
@@ -4770,13 +4767,13 @@
         <v>27</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C249" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D249" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>7</v>
@@ -4787,13 +4784,13 @@
         <v>27</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C250" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D250" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>7</v>
@@ -4804,13 +4801,13 @@
         <v>27</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C251" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D251" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>7</v>
@@ -4821,13 +4818,13 @@
         <v>27</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C252" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D252" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E252" s="1" t="s">
         <v>7</v>
@@ -4838,462 +4835,20 @@
         <v>27</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C253" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D253" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A254" t="s">
-        <v>27</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C254" t="s">
-        <v>9</v>
-      </c>
-      <c r="D254" t="s">
-        <v>36</v>
-      </c>
-      <c r="E254" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A255" t="s">
-        <v>27</v>
-      </c>
-      <c r="B255" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C255" t="s">
-        <v>9</v>
-      </c>
-      <c r="D255" t="s">
-        <v>42</v>
-      </c>
-      <c r="E255" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A256" t="s">
-        <v>27</v>
-      </c>
-      <c r="B256" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C256" t="s">
-        <v>9</v>
-      </c>
-      <c r="D256" t="s">
-        <v>42</v>
-      </c>
-      <c r="E256" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A257" t="s">
-        <v>27</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C257" t="s">
-        <v>9</v>
-      </c>
-      <c r="D257" t="s">
-        <v>42</v>
-      </c>
-      <c r="E257" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A258" t="s">
-        <v>27</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C258" t="s">
-        <v>9</v>
-      </c>
-      <c r="D258" t="s">
-        <v>42</v>
-      </c>
-      <c r="E258" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A259" t="s">
-        <v>27</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C259" t="s">
-        <v>9</v>
-      </c>
-      <c r="D259" t="s">
-        <v>42</v>
-      </c>
-      <c r="E259" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A260" t="s">
-        <v>27</v>
-      </c>
-      <c r="B260" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C260" t="s">
-        <v>9</v>
-      </c>
-      <c r="D260" t="s">
-        <v>42</v>
-      </c>
-      <c r="E260" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A261" t="s">
-        <v>27</v>
-      </c>
-      <c r="B261" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C261" t="s">
-        <v>9</v>
-      </c>
-      <c r="D261" t="s">
-        <v>42</v>
-      </c>
-      <c r="E261" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A262" t="s">
-        <v>27</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C262" t="s">
-        <v>9</v>
-      </c>
-      <c r="D262" t="s">
-        <v>42</v>
-      </c>
-      <c r="E262" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A263" t="s">
-        <v>27</v>
-      </c>
-      <c r="B263" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C263" t="s">
-        <v>9</v>
-      </c>
-      <c r="D263" t="s">
-        <v>42</v>
-      </c>
-      <c r="E263" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A264" t="s">
-        <v>27</v>
-      </c>
-      <c r="B264" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C264" t="s">
-        <v>9</v>
-      </c>
-      <c r="D264" t="s">
-        <v>42</v>
-      </c>
-      <c r="E264" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A265" t="s">
-        <v>27</v>
-      </c>
-      <c r="B265" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C265" t="s">
-        <v>9</v>
-      </c>
-      <c r="D265" t="s">
-        <v>42</v>
-      </c>
-      <c r="E265" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A266" t="s">
-        <v>27</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C266" t="s">
-        <v>9</v>
-      </c>
-      <c r="D266" t="s">
-        <v>42</v>
-      </c>
-      <c r="E266" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A267" t="s">
-        <v>27</v>
-      </c>
-      <c r="B267" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C267" t="s">
-        <v>9</v>
-      </c>
-      <c r="D267" t="s">
-        <v>42</v>
-      </c>
-      <c r="E267" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A268" t="s">
-        <v>27</v>
-      </c>
-      <c r="B268" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C268" t="s">
-        <v>9</v>
-      </c>
-      <c r="D268" t="s">
-        <v>42</v>
-      </c>
-      <c r="E268" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A269" t="s">
-        <v>27</v>
-      </c>
-      <c r="B269" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C269" t="s">
-        <v>9</v>
-      </c>
-      <c r="D269" t="s">
-        <v>42</v>
-      </c>
-      <c r="E269" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A270" t="s">
-        <v>27</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C270" t="s">
-        <v>9</v>
-      </c>
-      <c r="D270" t="s">
-        <v>42</v>
-      </c>
-      <c r="E270" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A271" t="s">
-        <v>27</v>
-      </c>
-      <c r="B271" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C271" t="s">
-        <v>9</v>
-      </c>
-      <c r="D271" t="s">
-        <v>42</v>
-      </c>
-      <c r="E271" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A272" t="s">
-        <v>27</v>
-      </c>
-      <c r="B272" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C272" t="s">
-        <v>43</v>
-      </c>
-      <c r="D272" t="s">
-        <v>44</v>
-      </c>
-      <c r="E272" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A273" t="s">
-        <v>27</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C273" t="s">
-        <v>43</v>
-      </c>
-      <c r="D273" t="s">
-        <v>44</v>
-      </c>
-      <c r="E273" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A274" t="s">
-        <v>27</v>
-      </c>
-      <c r="B274" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C274" t="s">
-        <v>43</v>
-      </c>
-      <c r="D274" t="s">
-        <v>44</v>
-      </c>
-      <c r="E274" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A275" t="s">
-        <v>27</v>
-      </c>
-      <c r="B275" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C275" t="s">
-        <v>43</v>
-      </c>
-      <c r="D275" t="s">
-        <v>44</v>
-      </c>
-      <c r="E275" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A276" t="s">
-        <v>27</v>
-      </c>
-      <c r="B276" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C276" t="s">
-        <v>43</v>
-      </c>
-      <c r="D276" t="s">
-        <v>44</v>
-      </c>
-      <c r="E276" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A277" t="s">
-        <v>27</v>
-      </c>
-      <c r="B277" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C277" t="s">
-        <v>43</v>
-      </c>
-      <c r="D277" t="s">
-        <v>44</v>
-      </c>
-      <c r="E277" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A278" t="s">
-        <v>27</v>
-      </c>
-      <c r="B278" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C278" t="s">
-        <v>43</v>
-      </c>
-      <c r="D278" t="s">
-        <v>44</v>
-      </c>
-      <c r="E278" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A279" t="s">
-        <v>27</v>
-      </c>
-      <c r="B279" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C279" t="s">
-        <v>43</v>
-      </c>
-      <c r="D279" t="s">
-        <v>44</v>
-      </c>
-      <c r="E279" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E271" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E253" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
